--- a/stories/arbres/ATOM-LAN.MOT.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Violette est dans le salon avec maman. Sur le tapis : une pomme, une banane, une chaussette, un bonnet. Maman dit : on nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Violette met la pomme et la banane dans le panier. Catégorie des fruits. Elle met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
+          <t>Violette est dans le salon avec maman. Sur le tapis : une pomme, une banane, une chaussette, un bonnet. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Violette met la pomme et la banane dans le panier. Catégorie des fruits. Elle met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Violette est dans le salon avec maman. Sur le tapis : une pomme, une banane, une chaussette, un bonnet.
+maman|On nomme. On classe.
+narrateur|Une catégorie pour les fruits. Une catégorie pour les habits. Violette met la pomme et la banane dans le panier. Catégorie des fruits. Elle met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Violette range pomme et chaussette. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Violette a classé. Une catégorie pour les fruits. Une pour les habits.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Violette croque la pomme. Maman plie le bonnet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Une catégorie pour les fruits. Une catégorie pour les habits. Violette met la pomme et la banane dans le panier. Catégorie des fruits. Elle met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Violette range pomme et chaussette. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Violette a classé. Une catégorie pour les fruits. Une pour les habits.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Violette croque la pomme. Maman plie le bonnet.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.MOT.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Violette classe au salon</t>
+          <t>Le panier et la chaise de Sarah</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LAN.NOM.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La pluie tapote la vitre. Sarah met pomme et banane dans le panier. Chaussette et bonnet sur la chaise. Deux catégories.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Violette est dans le salon avec maman. Sur le tapis : une pomme, une banane, une chaussette, un bonnet. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Violette met la pomme et la banane dans le panier. Catégorie des fruits. Elle met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
+          <t>La pluie tapote la vitre du salon. Des gouttes glissent en file. Le radiateur est tiède sous la main. Un panier à linge sent le savon. Une chaussette jaune pend au bord. Un bonnet gris dort sur le fauteuil. Sur la table, une pomme brille. Une banane jaunit tout près. Tu as vu la vitre, Sarah ? Oui, maman. Ça tapote. On reste au salon, tout au chaud. En ce moment, Sarah s'assoit sur le tapis. Le tapis est épais et doux. Maman pose un panier d'osier. Elle tire une chaise tout près. On nomme. Puis on classe. Une catégorie pour les fruits. Une catégorie pour les habits. Les fruits ensemble ? Oui. On les met ensemble. Sarah prend la pomme. Elle est lisse et froide. Une pomme. Oui. C'est un fruit. Sarah la pose dans le panier. Elle prend la banane. La peau est un peu douce. Une banane. Encore un fruit. Sarah la met avec la pomme. Catégorie des fruits. Tu les as mis ensemble. Bravo, Sarah. Sarah prend la chaussette jaune. Elle est encore un peu chaude. Une chaussette. Oui. C'est un habit. Sarah la pose sur la chaise. Elle prend le bonnet gris. La laine gratte un tout petit peu. Un bonnet. Encore un habit. Sarah le met avec la chaussette. Catégorie des habits. Tu les as mis ensemble. C'est du bon travail. Deux catégories. Oui. Fruits. Habits. Tu as classé. La pluie tapote encore. On compte les fruits ? Une. Deux. Deux fruits dans le panier. Et les habits ? Une. Deux. Deux habits sur la chaise. Tu as nommé. Tu as classé. Le panier sent la pomme. Oui. Et la chaise a le bonnet. Une goutte glisse encore sur la vitre. Elle fait un petit trait. Tu as fini de classer ? Oui, maman. Bravo. Les fruits ensemble. Les habits ensemble. Le tapis reste doux sous les genoux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1329,82 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Violette est dans le salon avec maman. Sur le tapis : une pomme, une banane, une chaussette, un bonnet.
-maman|On nomme. On classe.
-narrateur|Une catégorie pour les fruits. Une catégorie pour les habits. Violette met la pomme et la banane dans le panier. Catégorie des fruits. Elle met la chaussette et le bonnet sur la chaise. Catégorie des habits.</t>
+          <t>narrateur|La pluie tapote la vitre du salon.
+narrateur|Des gouttes glissent en file.
+narrateur|Le radiateur est tiède sous la main.
+narrateur|Un panier à linge sent le savon.
+narrateur|Une chaussette jaune pend au bord.
+narrateur|Un bonnet gris dort sur le fauteuil.
+narrateur|Sur la table, une pomme brille.
+narrateur|Une banane jaunit tout près.
+maman|Tu as vu la vitre, Sarah ?
+enfant-f|Oui, maman.
+enfant-f|Ça tapote.
+maman|On reste au salon, tout au chaud.
+narrateur|En ce moment, Sarah s'assoit sur le tapis.
+narrateur|Le tapis est épais et doux.
+narrateur|Maman pose un panier d'osier.
+narrateur|Elle tire une chaise tout près.
+maman|On nomme.
+maman|Puis on classe.
+maman|Une catégorie pour les fruits.
+maman|Une catégorie pour les habits.
+enfant-f|Les fruits ensemble ?
+maman|Oui.
+maman|On les met ensemble.
+narrateur|Sarah prend la pomme.
+narrateur|Elle est lisse et froide.
+enfant-f|Une pomme.
+maman|Oui.
+maman|C'est un fruit.
+narrateur|Sarah la pose dans le panier.
+narrateur|Elle prend la banane.
+narrateur|La peau est un peu douce.
+enfant-f|Une banane.
+maman|Encore un fruit.
+narrateur|Sarah la met avec la pomme.
+maman|Catégorie des fruits.
+maman|Tu les as mis ensemble.
+maman|Bravo, Sarah.
+narrateur|Sarah prend la chaussette jaune.
+narrateur|Elle est encore un peu chaude.
+enfant-f|Une chaussette.
+maman|Oui.
+maman|C'est un habit.
+narrateur|Sarah la pose sur la chaise.
+narrateur|Elle prend le bonnet gris.
+narrateur|La laine gratte un tout petit peu.
+enfant-f|Un bonnet.
+maman|Encore un habit.
+narrateur|Sarah le met avec la chaussette.
+maman|Catégorie des habits.
+maman|Tu les as mis ensemble.
+maman|C'est du bon travail.
+enfant-f|Deux catégories.
+maman|Oui.
+maman|Fruits.
+maman|Habits.
+maman|Tu as classé.
+narrateur|La pluie tapote encore.
+maman|On compte les fruits ?
+enfant-f|Une. Deux.
+maman|Deux fruits dans le panier.
+maman|Et les habits ?
+enfant-f|Une. Deux.
+maman|Deux habits sur la chaise.
+maman|Tu as nommé.
+maman|Tu as classé.
+enfant-f|Le panier sent la pomme.
+maman|Oui.
+maman|Et la chaise a le bonnet.
+narrateur|Une goutte glisse encore sur la vitre.
+narrateur|Elle fait un petit trait.
+maman|Tu as fini de classer ?
+enfant-f|Oui, maman.
+maman|Bravo.
+maman|Les fruits ensemble.
+maman|Les habits ensemble.
+narrateur|Le tapis reste doux sous les genoux.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1432,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Violette range pomme et chaussette. Que fait-elle ?</t>
+          <t>Sarah range pomme et chaussette. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1588,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Violette range pomme et chaussette. Que fait-elle ?</t>
+          <t>narrateur|Sarah range pomme et chaussette.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1617,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Violette a classé. Une catégorie pour les fruits. Une pour les habits.</t>
+          <t>Sarah a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Sarah. Pomme et banane. Chaussette et bonnet. Oui. Tu as fait du bon travail. La pomme brille encore dans le panier. Le bonnet reste sur la chaise.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1761,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Violette a classé. Une catégorie pour les fruits. Une pour les habits.</t>
+          <t>narrateur|Sarah a classé.
+narrateur|Une catégorie pour les fruits.
+narrateur|Une catégorie pour les habits.
+maman|Tu as mis ensemble.
+maman|Bravo, Sarah.
+enfant-f|Pomme et banane.
+enfant-f|Chaussette et bonnet.
+maman|Oui.
+maman|Tu as fait du bon travail.
+narrateur|La pomme brille encore dans le panier.
+narrateur|Le bonnet reste sur la chaise.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1799,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Violette croque la pomme. Maman plie le bonnet.</t>
+          <t>Sarah croque un petit bout de pomme. Ça croque tout fort. Tu as fini ta bouchée ? Oui, maman. Je plie le bonnet. Tu as classé les fruits et les habits. Dans le panier. Sur la chaise. Bravo. La vitre est encore mouillée. Le radiateur reste tiède.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,7 +1935,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Violette croque la pomme. Maman plie le bonnet.</t>
+          <t>narrateur|Sarah croque un petit bout de pomme.
+narrateur|Ça croque tout fort.
+maman|Tu as fini ta bouchée ?
+enfant-f|Oui, maman.
+maman|Je plie le bonnet.
+maman|Tu as classé les fruits et les habits.
+enfant-f|Dans le panier.
+enfant-f|Sur la chaise.
+maman|Bravo.
+narrateur|La vitre est encore mouillée.
+narrateur|Le radiateur reste tiède.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1862,7 +1973,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La chaussette jaune sèche. Tu as nommé. Tu as classé. Deux catégories. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,7 +2113,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La chaussette jaune sèche.
+maman|Tu as nommé.
+maman|Tu as classé.
+enfant-f|Deux catégories.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2024,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2177,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-09.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La pluie tapote la vitre du salon. Des gouttes glissent en file. Le radiateur est tiède sous la main. Un panier à linge sent le savon. Une chaussette jaune pend au bord. Un bonnet gris dort sur le fauteuil. Sur la table, une pomme brille. Une banane jaunit tout près. Tu as vu la vitre, Sarah ? Oui, maman. Ça tapote. On reste au salon, tout au chaud. En ce moment, Sarah s'assoit sur le tapis. Le tapis est épais et doux. Maman pose un panier d'osier. Elle tire une chaise tout près. On nomme. Puis on classe. Une catégorie pour les fruits. Une catégorie pour les habits. Les fruits ensemble ? Oui. On les met ensemble. Sarah prend la pomme. Elle est lisse et froide. Une pomme. Oui. C'est un fruit. Sarah la pose dans le panier. Elle prend la banane. La peau est un peu douce. Une banane. Encore un fruit. Sarah la met avec la pomme. Catégorie des fruits. Tu les as mis ensemble. Bravo, Sarah. Sarah prend la chaussette jaune. Elle est encore un peu chaude. Une chaussette. Oui. C'est un habit. Sarah la pose sur la chaise. Elle prend le bonnet gris. La laine gratte un tout petit peu. Un bonnet. Encore un habit. Sarah le met avec la chaussette. Catégorie des habits. Tu les as mis ensemble. C'est du bon travail. Deux catégories. Oui. Fruits. Habits. Tu as classé. La pluie tapote encore. On compte les fruits ? Une. Deux. Deux fruits dans le panier. Et les habits ? Une. Deux. Deux habits sur la chaise. Tu as nommé. Tu as classé. Le panier sent la pomme. Oui. Et la chaise a le bonnet. Une goutte glisse encore sur la vitre. Elle fait un petit trait. Tu as fini de classer ? Oui, maman. Bravo. Les fruits ensemble. Les habits ensemble. Le tapis reste doux sous les genoux.</t>
+          <t>La pluie tapote la vitre du salon. Des gouttes glissent en file. Le radiateur est tiède sous la main. Un panier à linge sent le savon. Une chaussette jaune pend au bord. Un bonnet gris dort sur le fauteuil. Sur la table, une pomme brille. Une banane jaunit tout près. Tu as vu la vitre, Sarah ? Oui, maman. Ça tapote. On reste au salon, tout au chaud. En ce moment, Sarah s'assoit sur le tapis. Le tapis est épais et doux. Maman pose un panier d'osier. Elle tire une chaise tout près. On nomme. Puis on classe. Une catégorie pour les fruits. Une catégorie pour les habits. Les fruits ensemble ? Oui. On les met ensemble. Sarah prend la pomme. Elle est lisse et froide. Une pomme. Oui. C'est un fruit. Sarah la pose dans le panier. Elle prend la banane. La peau est un peu douce. Une banane. Encore un fruit. Sarah la met avec la pomme. Catégorie des fruits. Tu les as mis ensemble. Bravo, Sarah. Sarah prend la chaussette jaune. Elle est encore un peu chaude. Une chaussette. Oui. C'est un habit. Sarah la pose sur la chaise. Elle prend le bonnet gris. La laine gratte un tout petit peu. Un bonnet. Encore un habit. Sarah le met avec la chaussette. Catégorie des habits. Tu les as mis ensemble. Deux catégories. Oui. Fruits. Habits. Tu as classé. La pluie tapote encore. On compte les fruits ? Une. Deux. Deux fruits dans le panier. Et les habits ? Une. Deux. Deux habits sur la chaise. Tu as nommé. Tu as classé. Le panier sent la pomme. Oui. Et la chaise a le bonnet. Une goutte glisse encore sur la vitre. Elle fait un petit trait. Tu as fini de classer ? Oui, maman. Bravo. Les fruits ensemble. Les habits ensemble. Le tapis reste doux sous les genoux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Violette est dans le salon avec maman. Sur le tapis : une pomme, une banane, une chaussette, un bonnet. Maman dit : on nomme. On classe. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une catégorie pour les habits. Violette met la pomme et la banane dans le panier. Catégorie des fruits. Elle met la chaussette et le bonnet sur la chaise. Catégorie des habits.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pluie tapote la vitre du salon. Des gouttes glissent en file. Le radiateur est tiède sous la main. Un panier à linge sent le savon. Une chaussette jaune pend au bord. Un bonnet gris dort sur le fauteuil. Sur la table, une pomme brille. Une banane jaunit tout près. Tu as vu la vitre, Sarah ? Oui, maman. Ça tapote. On reste au salon, tout au chaud. En ce moment, Sarah s'assoit sur le tapis. Le tapis est épais et doux. Maman pose un panier d'osier. Elle tire une chaise tout près. On nomme. Puis on classe. Une catégorie pour les fruits. Une catégorie pour les habits. Les fruits ensemble ? Oui. On les met ensemble. Sarah prend la pomme. Elle est lisse et froide. Une pomme. Oui. C'est un fruit. Sarah la pose dans le panier. Elle prend la banane. La peau est un peu douce. Une banane. Encore un fruit. Sarah la met avec la pomme. Catégorie des fruits. Tu les as mis ensemble. Bravo, Sarah. Sarah prend la chaussette jaune. Elle est encore un peu chaude. Une chaussette. Oui. C'est un habit. Sarah la pose sur la chaise. Elle prend le bonnet gris. La laine gratte un tout petit peu. Un bonnet. Encore un habit. Sarah le met avec la chaussette. Catégorie des habits. Tu les as mis ensemble. Deux catégories. Oui. Fruits. Habits. Tu as classé. La pluie tapote encore. On compte les fruits ? Une. Deux. Deux fruits dans le panier. Et les habits ? Une. Deux. Deux habits sur la chaise. Tu as nommé. Tu as classé. Le panier sent la pomme. Oui. Et la chaise a le bonnet. Une goutte glisse encore sur la vitre. Elle fait un petit trait. Tu as fini de classer ? Oui, maman. Bravo. Les fruits ensemble. Les habits ensemble. Le tapis reste doux sous les genoux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1379,7 +1379,6 @@
 narrateur|Sarah le met avec la chaussette.
 maman|Catégorie des habits.
 maman|Tu les as mis ensemble.
-maman|C'est du bon travail.
 enfant-f|Deux catégories.
 maman|Oui.
 maman|Fruits.
@@ -1407,7 +1406,6 @@
 narrateur|Le tapis reste doux sous les genoux.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1437,7 +1435,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Violette range pomme et chaussette. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah range pomme et chaussette. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1592,7 +1590,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1617,12 +1614,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Sarah. Pomme et banane. Chaussette et bonnet. Oui. Tu as fait du bon travail. La pomme brille encore dans le panier. Le bonnet reste sur la chaise.</t>
+          <t>Sarah a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Sarah. Pomme et banane. Chaussette et bonnet. Oui. La pomme brille encore dans le panier. Le bonnet reste sur la chaise.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Violette a classé. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une pour les habits.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a classé. Une catégorie pour les fruits. Une catégorie pour les habits. Tu as mis ensemble. Bravo, Sarah. Pomme et banane. Chaussette et bonnet. Oui. La pomme brille encore dans le panier. Le bonnet reste sur la chaise.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1769,12 +1766,10 @@
 enfant-f|Pomme et banane.
 enfant-f|Chaussette et bonnet.
 maman|Oui.
-maman|Tu as fait du bon travail.
 narrateur|La pomme brille encore dans le panier.
 narrateur|Le bonnet reste sur la chaise.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1804,7 +1799,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Violette croque la pomme. Maman plie le bonnet.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah croque un petit bout de pomme. Ça croque tout fort. Tu as fini ta bouchée ? Oui, maman. Je plie le bonnet. Tu as classé les fruits et les habits. Dans le panier. Sur la chaise. Bravo. La vitre est encore mouillée. Le radiateur reste tiède.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1948,7 +1943,6 @@
 narrateur|Le radiateur reste tiède.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1973,12 +1967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La chaussette jaune sèche. Tu as nommé. Tu as classé. Deux catégories. L'histoire est finie.</t>
+          <t>La chaussette jaune sèche. Tu as nommé. Tu as classé. Deux catégories.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La chaussette jaune sèche. Tu as nommé. Tu as classé. Deux catégories.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2116,11 +2110,9 @@
           <t>narrateur|La chaussette jaune sèche.
 maman|Tu as nommé.
 maman|Tu as classé.
-enfant-f|Deux catégories.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+enfant-f|Deux catégories.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2139,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2184,6 +2176,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-09.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, jour de pluie</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Violette, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
